--- a/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
@@ -707,6 +707,9 @@
       <c r="C31" t="str">
         <v>759_芍药红富士_Kansas_undefined_10stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -765,7 +768,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0453516172112204566131561520253514112330301531010301501000</v>
+        <v>045351617211220456613156152025351411233030153101030150100100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -711,9 +711,467 @@
         <v>100</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>15</v>
+      </c>
+      <c r="C32" t="str">
+        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>13</v>
+      </c>
+      <c r="C35" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>14</v>
+      </c>
+      <c r="C36" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>15</v>
+      </c>
+      <c r="C37" t="str">
+        <v>872_洋牡丹棉花糖_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>839_洋牡丹洋葱_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>16</v>
+      </c>
+      <c r="C39" t="str">
+        <v>681_锦鲤橙_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>682_锦鲤粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>840_洋牡丹塞纳河_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>882_乒乓菊黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>756_雪花松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>849_婚庆卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>17</v>
+      </c>
+      <c r="C45" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>18</v>
+      </c>
+      <c r="C47" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>19</v>
+      </c>
+      <c r="C48" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>20</v>
+      </c>
+      <c r="C49" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>21</v>
+      </c>
+      <c r="C50" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>22</v>
+      </c>
+      <c r="C54" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>23</v>
+      </c>
+      <c r="C57" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>24</v>
+      </c>
+      <c r="C58" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>839_洋牡丹洋葱_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>863_干花文竹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>362_蓬莱松_Asparagus_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>1</v>
+      </c>
+      <c r="C63" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2</v>
+      </c>
+      <c r="C64" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F64" t="str">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F65" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>3</v>
+      </c>
+      <c r="C68" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>589_洋牡丹香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>4</v>
+      </c>
+      <c r="C71" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F71" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>662_大丽花 白_undefined_undefined_5stems</v>
+      </c>
+      <c r="F72" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F73" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>5</v>
+      </c>
+      <c r="C74" t="str">
+        <v>662_大丽花 白_undefined_undefined_5stems</v>
+      </c>
+      <c r="F74" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F75" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+      </c>
+      <c r="F76" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" t="str">
+        <v>641_绿枫叶_maple leaf_undefined_1bunch</v>
+      </c>
+      <c r="F77" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>6</v>
+      </c>
+      <c r="C78" t="str">
+        <v>324_小手球单瓣_Spiraea flower_undefined_1bunch</v>
+      </c>
+      <c r="F78" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="C79" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F79" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -768,7 +1226,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>045351617211220456613156152025351411233030153101030150100100</v>
+        <v>04535161721122045661315615202535141123303015310103015010010040101140403020101037545102432343514.52510501912503312191810104746252520123020231551020525301550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
@@ -1168,6 +1168,9 @@
       <c r="C81" t="str">
         <v>300_白星_White Gypso_ gypsophila_1kg</v>
       </c>
+      <c r="F81" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1226,7 +1229,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>04535161721122045661315615202535141123303015310103015010010040101140403020101037545102432343514.52510501912503312191810104746252520123020231551020525301550</v>
+        <v>04535161721122045661315615202535141123303015310103015010010040101140403020101037545102432343514.52510501912503312191810104746252520123020231551020525301551</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1172,9 +1172,90 @@
         <v>1</v>
       </c>
     </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F82" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>348_万年青_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F83" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>7</v>
+      </c>
+      <c r="C84" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F84" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F85" t="str">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="str">
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
+      </c>
+      <c r="F86" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>348_万年青_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F87" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>8</v>
+      </c>
+      <c r="C88" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F88" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>10</v>
+      </c>
+      <c r="C89" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F89" t="str">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="str">
+        <v>827_豌豆花白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F90" t="str">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L90"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1229,7 +1310,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>04535161721122045661315615202535141123303015310103015010010040101140403020101037545102432343514.52510501912503312191810104746252520123020231551020525301551</v>
+        <v>04535161721122045661315615202535141123303015310103015010010040101140403020101037545102432343514.52510501912503312191810104746252520123020231551020525301551402050170510353612</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-3-3.xlsx
@@ -1312,6 +1312,9 @@
       <c r="G2" t="str">
         <v>04535161721122045661315615202535141123303015310103015010010040101140403020101037545102432343514.52510501912503312191810104746252520123020231551020525301551402050170510353612</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
